--- a/docs/sheets/Wieサイト更新シート.xlsx
+++ b/docs/sheets/Wieサイト更新シート.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -528,110 +528,124 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1件ごとに詳細ページができます。開催日時・場所・参加費・定員・申込方法・本文は、書いた項目だけページに出ます（空欄でOK）。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>申込方法に https:// で始まるURL（申込フォームなど）を書くと、「申し込む」ボタンになります。本文は改行・空行もそのまま反映されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>■ 写真</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>活動内容ページやサービスページに使う写真です。「載せる場所」は下の候補から選んでください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>候補：学習会・セミナー／つながる会／働き方相談室／暮らしとお金の相談／力を持ち寄るプロジェクト／デザイン制作／税務会計サポート</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>写っている人に掲載の許可をもらった写真だけを入れてください。</t>
+          <t>活動内容ページやサービスページに使う写真です。「載せる場所」は下の候補から選んでください。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>候補：学習会・セミナー／つながる会／働き方相談室／暮らしとお金の相談／力を持ち寄るプロジェクト／デザイン制作／税務会計サポート</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>写っている人に掲載の許可をもらった写真だけを入れてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>名前・連絡先・書類の中身などが写り込んでいないかも確認してください。</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>■ サービス料金</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>サービスごとの料金表です。上から順にサイトに並びます。</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>正式に決まった料金は「確定」を ○ にします。そのサービスの行がすべて ○ になると、サイトの「サンプルです」の表示が消えます。</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>■ リンク</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>ラジオなどのURLが決まったら貼ってください。</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>■ 写真フォルダへの入れ方</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1. 「Wieサイト写真」フォルダに写真を入れる（スマホの写真そのままでOK。iPhoneの場合はJPEGで保存したもの）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2. ドライブに表示されているファイル名（例：IMG_1234.jpg）を、このシートの「写真」の欄に書く</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
+        <is>
+          <t>1. 「Wieサイト写真」フォルダに写真を入れる（スマホの写真そのままでOK。iPhoneの場合はJPEGで保存したもの）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2. ドライブに表示されているファイル名（例：IMG_1234.jpg）を、このシートの「写真」の欄に書く</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>※ 写真のリンクを貼っても大丈夫です</t>
         </is>
@@ -648,7 +662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -660,6 +674,12 @@
     <col width="21.6" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="37.8" customWidth="1" min="9" max="9"/>
+    <col width="43.2" customWidth="1" min="10" max="10"/>
+    <col width="12.6" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="14.4" customWidth="1" min="14" max="14"/>
+    <col width="43.2" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -708,6 +728,36 @@
           <t>メモ（サイトには出ません）</t>
         </is>
       </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>開催日時</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>参加費</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>定員</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>申込方法</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>本文</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -751,6 +801,37 @@
           <t>「例」の行はサイトに出ません</t>
         </is>
       </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>2026.12.06（土）10:00〜11:45</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>札幌エルプラザ</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>500円</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>10名</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>公式LINEから</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>雑談・相談OKの交流会です。
+お気軽にどうぞ。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -794,6 +875,12 @@
           <t>リンクを入れるとタイトルがリンクになります</t>
         </is>
       </c>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -928,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.2" customWidth="1" min="1" max="1"/>
@@ -978,17 +1065,17 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>無料</t>
+          <t>3300円</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>オンライン</t>
+          <t>オンライン・対面</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>○</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1092,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>3,000円</t>
+          <t>5500円</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1015,29 +1102,29 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>×</t>
+          <t>○</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>働き方相談室</t>
+          <t>暮らしとお金の相談</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>継続相談（60分×3回）</t>
+          <t>個別相談（60分）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>8,000円</t>
+          <t>5500円</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>3か月以内</t>
+          <t>対面・オンライン</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -1054,17 +1141,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>個別相談（60分）</t>
+          <t>暮らしのかかりつけ</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>3,000円</t>
+          <t>月額 5,000円〜</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>対面・オンライン</t>
+          <t>月1回の面談を含む</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1081,17 +1168,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>暮らしのかかりつけ</t>
+          <t>専門家へのおつなぎ</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>月額 5,000円〜</t>
+          <t>無料</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>月1回の面談を含む</t>
+          <t>専門家への相談料は別途</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1103,22 +1190,22 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>暮らしとお金の相談</t>
+          <t>デザイン制作</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>専門家へのおつなぎ</t>
+          <t>チラシ（A4片面）</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>無料</t>
+          <t>20,000円〜</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>専門家への相談料は別途</t>
+          <t>修正2回まで含む</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1135,12 +1222,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>チラシ（A4片面）</t>
+          <t>チラシ（A4両面）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>20,000円〜</t>
+          <t>30,000円〜</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1162,17 +1249,17 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>チラシ（A4両面）</t>
+          <t>パンフレット（4ページ）</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>30,000円〜</t>
+          <t>50,000円〜</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>修正2回まで含む</t>
+          <t>構成・文章整理を含む</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1189,17 +1276,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>パンフレット（4ページ）</t>
+          <t>SNS投稿画像</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>50,000円〜</t>
+          <t>5,000円〜／1枚</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>構成・文章整理を含む</t>
+          <t>複数枚はお見積り</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1216,17 +1303,17 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>SNS投稿画像</t>
+          <t>名刺・ショップカード</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>5,000円〜／1枚</t>
+          <t>10,000円〜</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>複数枚はお見積り</t>
+          <t>片面デザイン</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1238,22 +1325,22 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>デザイン制作</t>
+          <t>税務会計サポート</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>名刺・ショップカード</t>
+          <t>記帳代行</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>10,000円〜</t>
+          <t>月額 15,000円〜</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>片面デザイン</t>
+          <t>仕訳100件まで</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1270,17 +1357,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>記帳代行</t>
+          <t>書類の整理</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>月額 10,000円〜</t>
+          <t>5,000円〜／1回</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>仕訳100件まで</t>
+          <t>量によってお見積り</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1297,47 +1384,20 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>書類の整理</t>
+          <t>会計ソフトの導入サポート</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>5,000円〜／1回</t>
+          <t>15,000円〜</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>量によってお見積り</t>
+          <t>初期設定と操作説明</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>×</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>税務会計サポート</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>会計ソフトの導入サポート</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>15,000円〜</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>初期設定と操作説明</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>×</t>
         </is>
@@ -1423,7 +1483,11 @@
           <t>ラジオ</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>https://stand.fm/channels/67a4562311be6ce817443e42</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
